--- a/results/full_birds_summary/birds_ScoreVector_summary.xlsx
+++ b/results/full_birds_summary/birds_ScoreVector_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG12"/>
+  <dimension ref="A1:AG14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2429,6 +2429,340 @@
       <c r="AG12" t="inlineStr">
         <is>
           <t>0.1561±0.0176</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ecc</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>nan±nan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>nan±nan</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>nan±nan</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>nan±nan</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0.9150±0.0109</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.8594±0.0263</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.8060±0.0370</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.7378±0.0243</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.5598±0.0258</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0.3945±0.0507</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0.2917±0.0509</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>0.2141±0.0374</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0.5909±0.0686</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0.4655±0.0713</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>0.3319±0.0704</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>0.1964±0.0433</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>1.5690±0.2932</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>2.1907±0.3897</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>2.7960±0.3937</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>3.6679±0.5487</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>0.8447±0.0076</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>0.8070±0.0138</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>0.7573±0.0196</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>0.6916±0.0250</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>0.6248±0.0418</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>0.6636±0.0512</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>0.7209±0.0621</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>0.8062±0.0426</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>0.0618±0.0057</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>0.0882±0.0120</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>0.1171±0.0139</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>0.1583±0.0176</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>mlknn</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>nan±nan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>nan±nan</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>nan±nan</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>nan±nan</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0.7450±0.0122</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.5674±0.0242</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.5386±0.0274</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.5261±0.0270</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.0948±0.0029</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0.0674±0.0071</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0.0655±0.0086</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>0.0645±0.0074</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0.1303±0.0157</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0.0683±0.0110</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0.0644±0.0143</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0.0599±0.0100</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>3.8791±0.5298</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>5.3296±0.7072</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>5.5516±0.6729</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>5.5836±0.7204</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0.6357±0.0318</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>0.5903±0.0355</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>0.5857±0.0329</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>0.5872±0.0335</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>0.8977±0.0237</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>0.9333±0.0258</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>0.9361±0.0311</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>0.9355±0.0188</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>0.1768±0.0181</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>0.2529±0.0288</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>0.2627±0.0250</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>0.2634±0.0286</t>
         </is>
       </c>
     </row>
